--- a/data/api_test_cases.xlsx
+++ b/data/api_test_cases.xlsx
@@ -12,6 +12,7 @@
     <sheet name="headers" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="cookies" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="字段说明" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="api" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2081,4 +2082,1869 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q35"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>case_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>case_name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>priority</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>method</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>path</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>params</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>headers</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>json_body</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>expected_status</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>expected_code</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>assert_type</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>assert_field</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>assert_value</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>extract_var</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>extract_field</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>remark</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>AI_GET_api_users?page=2_002</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>正常获取用户列表第二页</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>/api/users?page=2</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>200</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>eq</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>AI生成 | 正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>AI_GET_api_users?page=0_003</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>边界测试：页码为0</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>/api/users?page=0</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>200</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>eq</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>AI生成 | 边界</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>AI_GET_api_users?page=999999_004</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>边界测试：页码为极大值</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>/api/users?page=999999</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>200</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>eq</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>AI生成 | 边界</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>AI_GET_api_users?page=-1_005</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>异常测试：页码为负数</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>/api/users?page=-1</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>200</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>eq</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>AI生成 | 异常</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>AI_GET_api_users?page=abc_006</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>异常测试：页码为非数字字符</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>/api/users?page=abc</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>200</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>eq</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>AI生成 | 异常</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>AI_GET_api_users?page=1.5_007</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>异常测试：页码为浮点数</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>/api/users?page=1.5</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>200</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>eq</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>AI生成 | 异常</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>AI_GET_api_users?page=1' OR '1'='1_008</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>安全测试：SQL注入尝试（页码参数）</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>/api/users?page=1' OR '1'='1</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>200</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>eq</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>AI生成 | 安全</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>AI_GET_api_users?page=1 UNION SELECT username, password FROM users_009</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>安全测试：SQL注入尝试（联合查询）</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>/api/users?page=1 UNION SELECT username, password FROM users</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>200</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>eq</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>AI生成 | 安全</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>AI_GET_api_users?page=&lt;script&gt;alert('xss')&lt;_script&gt;_010</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>安全测试：XSS payload尝试</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>/api/users?page=&lt;script&gt;alert('xss')&lt;/script&gt;</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>200</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>eq</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>AI生成 | 安全</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>AI_GET_api_users?page=_011</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>边界测试：页码为空值</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>/api/users?page=</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>200</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>eq</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>AI生成 | 边界</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>AI_GET_api_users?page=1&amp;page=2_012</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>异常测试：多个page参数</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>/api/users?page=1&amp;page=2</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>200</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>eq</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>AI生成 | 异常</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>AI_GET_api_users?page=2_002</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>正常获取用户列表第二页</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>/api/users?page=2</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>200</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>eq</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>AI生成 | 正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>AI_GET_api_users?page=1_003</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>边界测试-页码为最小值1</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>/api/users?page=1</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>200</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>eq</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>AI生成 | 边界</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>AI_GET_api_users?page=999999_004</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>边界测试-页码为非常大的数（超出数据范围）</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>/api/users?page=999999</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>200</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>eq</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>AI生成 | 边界</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>AI_GET_api_users?page=0_005</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>异常测试-页码为0</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>/api/users?page=0</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>200</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>eq</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>AI生成 | 异常</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>AI_GET_api_users?page=-1_006</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>异常测试-页码为负数</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>/api/users?page=-1</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>200</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>eq</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>AI生成 | 异常</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>AI_GET_api_users?page=abc_007</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>异常测试-页码为非数字字符串</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>/api/users?page=abc</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>200</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>eq</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>AI生成 | 异常</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>AI_GET_api_users?page=1' OR '1'='1_008</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>安全测试-SQL注入尝试（通过页码参数）</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>/api/users?page=1' OR '1'='1</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>200</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>eq</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>AI生成 | 安全</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>AI_GET_api_users?page=&lt;script&gt;alert('xss')&lt;_script&gt;_009</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>安全测试-XSS payload尝试（通过页码参数）</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>/api/users?page=&lt;script&gt;alert('xss')&lt;/script&gt;</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>200</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>eq</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>AI生成 | 安全</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>AI_GET_api_users?page=2.5_010</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>边界测试-页码为浮点数</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>/api/users?page=2.5</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>200</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>eq</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>AI生成 | 边界</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>AI_GET_api_users?page=1&amp;other=value_011</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>正常测试-不存在的查询参数应被忽略</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>/api/users?page=1&amp;other=value</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>200</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>eq</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>AI生成 | 正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>AI_GET_api_users?page=1 UNION SELECT username, password FROM users_012</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>安全测试-额外的SQL注入payload（UNION SELECT）</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>/api/users?page=1 UNION SELECT username, password FROM users</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>200</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>eq</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>AI生成 | 安全</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>AI_GET_api_users_001</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>正常获取用户列表第一页</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>/api/users</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>{"Content-Type": "application/json"}</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="n">
+        <v>200</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>eq</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>AI生成 | 正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>AI_GET_api_users?page=2_002</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>正常获取用户列表第二页</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>/api/users?page=2</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>{"Content-Type": "application/json"}</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="n">
+        <v>200</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>eq</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>AI生成 | 正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>AI_GET_api_users?page=0_003</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>边界测试：页码为0</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>/api/users?page=0</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>{"Content-Type": "application/json"}</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="n">
+        <v>200</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>eq</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>AI生成 | 边界</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>AI_GET_api_users?page=999999_004</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>边界测试：页码为极大值</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>/api/users?page=999999</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>{"Content-Type": "application/json"}</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="n">
+        <v>200</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>eq</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>AI生成 | 边界</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>AI_GET_api_users?page=-1_005</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>异常测试：页码为负数</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>/api/users?page=-1</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>{"Content-Type": "application/json"}</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="n">
+        <v>200</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>eq</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>AI生成 | 异常</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>AI_GET_api_users?page=abc_006</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>异常测试：页码为非数字字符</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>/api/users?page=abc</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>{"Content-Type": "application/json"}</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="n">
+        <v>200</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>eq</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>AI生成 | 异常</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>AI_GET_api_users?page=1.5_007</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>异常测试：页码为浮点数</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>/api/users?page=1.5</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>{"Content-Type": "application/json"}</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="n">
+        <v>200</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>eq</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>AI生成 | 异常</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>AI_GET_api_users?page=1 OR 1=1_008</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>安全测试：SQL注入尝试（页码参数）</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>/api/users?page=1 OR 1=1</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>{"Content-Type": "application/json"}</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="n">
+        <v>200</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>eq</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>AI生成 | 安全</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>AI_GET_api_users?page=&lt;script&gt;alert('xss')&lt;_script&gt;_009</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>安全测试：XSS payload尝试（通过页码参数）</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>/api/users?page=&lt;script&gt;alert('xss')&lt;/script&gt;</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>{"Content-Type": "application/json"}</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="n">
+        <v>200</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>eq</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>AI生成 | 安全</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>AI_GET_api_users?page=.._.._.._etc_passwd_010</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>安全测试：路径遍历尝试</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>/api/users?page=../../../etc/passwd</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>{"Content-Type": "application/json"}</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="n">
+        <v>200</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>eq</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>AI生成 | 安全</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>AI_GET_api_users?page=_011</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>边界测试：页码为空字符串</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>/api/users?page=</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>{"Content-Type": "application/json"}</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="n">
+        <v>200</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>eq</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>AI生成 | 边界</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>AI_GET_api_users?page=1_012</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>正常测试：页码为1（最小有效值）</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>/api/users?page=1</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>{"Content-Type": "application/json"}</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="n">
+        <v>200</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>eq</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>AI生成 | 正常</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>